--- a/data/raw/documents.xlsx
+++ b/data/raw/documents.xlsx
@@ -3212,16 +3212,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -3244,7 +3236,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -3252,35 +3244,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3580,19 +3554,19 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3603,7 +3577,7 @@
       <c r="B2" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>100</v>
       </c>
       <c r="D2" t="s">
@@ -3620,7 +3594,7 @@
       <c r="B3" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>101</v>
       </c>
       <c r="D3" t="s">
@@ -3637,7 +3611,7 @@
       <c r="B4" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D4" t="s">
@@ -3654,7 +3628,7 @@
       <c r="B5" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>103</v>
       </c>
       <c r="D5" t="s">
@@ -3671,7 +3645,7 @@
       <c r="B6" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>104</v>
       </c>
       <c r="D6" t="s">
@@ -3688,7 +3662,7 @@
       <c r="B7" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D7" t="s">
@@ -3705,7 +3679,7 @@
       <c r="B8" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D8" t="s">
@@ -3722,7 +3696,7 @@
       <c r="B9" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>107</v>
       </c>
       <c r="D9" t="s">
@@ -3739,7 +3713,7 @@
       <c r="B10" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D10" t="s">
@@ -3756,7 +3730,7 @@
       <c r="B11" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>109</v>
       </c>
       <c r="D11" t="s">
@@ -3773,7 +3747,7 @@
       <c r="B12" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D12" t="s">
@@ -3790,7 +3764,7 @@
       <c r="B13" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>111</v>
       </c>
       <c r="D13" t="s">
@@ -3807,7 +3781,7 @@
       <c r="B14" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D14" t="s">
@@ -3824,7 +3798,7 @@
       <c r="B15" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D15" t="s">
@@ -3841,7 +3815,7 @@
       <c r="B16" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D16" t="s">
@@ -3858,7 +3832,7 @@
       <c r="B17" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D17" t="s">
@@ -3875,7 +3849,7 @@
       <c r="B18" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D18" t="s">
@@ -3892,7 +3866,7 @@
       <c r="B19" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>116</v>
       </c>
       <c r="D19" t="s">
@@ -3909,7 +3883,7 @@
       <c r="B20" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>117</v>
       </c>
       <c r="D20" t="s">
@@ -3926,7 +3900,7 @@
       <c r="B21" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>118</v>
       </c>
       <c r="D21" t="s">
@@ -3943,7 +3917,7 @@
       <c r="B22" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D22" t="s">
@@ -3960,7 +3934,7 @@
       <c r="B23" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D23" t="s">
@@ -3977,7 +3951,7 @@
       <c r="B24" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>121</v>
       </c>
       <c r="D24" t="s">
@@ -3994,7 +3968,7 @@
       <c r="B25" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>122</v>
       </c>
       <c r="D25" t="s">
@@ -4011,7 +3985,7 @@
       <c r="B26" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D26" t="s">
@@ -4028,7 +4002,7 @@
       <c r="B27" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D27" t="s">
@@ -4045,7 +4019,7 @@
       <c r="B28" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>125</v>
       </c>
       <c r="D28" t="s">
@@ -4062,7 +4036,7 @@
       <c r="B29" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D29" t="s">
@@ -4079,7 +4053,7 @@
       <c r="B30" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>127</v>
       </c>
       <c r="D30" t="s">
@@ -4096,7 +4070,7 @@
       <c r="B31" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>128</v>
       </c>
       <c r="D31" t="s">
@@ -4113,7 +4087,7 @@
       <c r="B32" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>129</v>
       </c>
       <c r="D32" t="s">
@@ -4130,7 +4104,7 @@
       <c r="B33" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>130</v>
       </c>
       <c r="D33" t="s">
@@ -4147,7 +4121,7 @@
       <c r="B34" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>131</v>
       </c>
       <c r="D34" t="s">
@@ -4164,7 +4138,7 @@
       <c r="B35" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>132</v>
       </c>
       <c r="D35" t="s">
@@ -4181,7 +4155,7 @@
       <c r="B36" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>133</v>
       </c>
       <c r="D36" t="s">
@@ -4198,7 +4172,7 @@
       <c r="B37" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>134</v>
       </c>
       <c r="D37" t="s">
@@ -4215,7 +4189,7 @@
       <c r="B38" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>135</v>
       </c>
       <c r="D38" t="s">
@@ -4232,7 +4206,7 @@
       <c r="B39" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>136</v>
       </c>
       <c r="D39" t="s">
@@ -4249,7 +4223,7 @@
       <c r="B40" t="s">
         <v>97</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D40" t="s">
@@ -4266,7 +4240,7 @@
       <c r="B41" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>138</v>
       </c>
       <c r="D41" t="s">
@@ -4283,7 +4257,7 @@
       <c r="B42" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D42" t="s">
@@ -4300,7 +4274,7 @@
       <c r="B43" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D43" t="s">
@@ -4317,7 +4291,7 @@
       <c r="B44" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D44" t="s">
@@ -4334,7 +4308,7 @@
       <c r="B45" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>141</v>
       </c>
       <c r="D45" t="s">
@@ -4351,7 +4325,7 @@
       <c r="B46" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D46" t="s">
@@ -4368,7 +4342,7 @@
       <c r="B47" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D47" t="s">
@@ -4385,7 +4359,7 @@
       <c r="B48" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>144</v>
       </c>
       <c r="D48" t="s">
@@ -4402,7 +4376,7 @@
       <c r="B49" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>145</v>
       </c>
       <c r="D49" t="s">
@@ -4419,7 +4393,7 @@
       <c r="B50" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>146</v>
       </c>
       <c r="D50" t="s">
@@ -4436,7 +4410,7 @@
       <c r="B51" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>147</v>
       </c>
       <c r="D51" t="s">
@@ -4453,7 +4427,7 @@
       <c r="B52" t="s">
         <v>97</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>148</v>
       </c>
       <c r="D52" t="s">
@@ -4470,7 +4444,7 @@
       <c r="B53" t="s">
         <v>97</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>149</v>
       </c>
       <c r="D53" t="s">
@@ -4487,7 +4461,7 @@
       <c r="B54" t="s">
         <v>97</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>149</v>
       </c>
       <c r="D54" t="s">
@@ -4504,7 +4478,7 @@
       <c r="B55" t="s">
         <v>97</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D55" t="s">
@@ -4521,7 +4495,7 @@
       <c r="B56" t="s">
         <v>98</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>151</v>
       </c>
       <c r="D56" t="s">
@@ -4538,7 +4512,7 @@
       <c r="B57" t="s">
         <v>97</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>152</v>
       </c>
       <c r="D57" t="s">
@@ -4555,7 +4529,7 @@
       <c r="B58" t="s">
         <v>99</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>153</v>
       </c>
       <c r="D58" t="s">
@@ -4572,7 +4546,7 @@
       <c r="B59" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>154</v>
       </c>
       <c r="D59" t="s">
@@ -4589,7 +4563,7 @@
       <c r="B60" t="s">
         <v>97</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>155</v>
       </c>
       <c r="D60" t="s">
@@ -4606,7 +4580,7 @@
       <c r="B61" t="s">
         <v>97</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>156</v>
       </c>
       <c r="D61" t="s">
@@ -4623,7 +4597,7 @@
       <c r="B62" t="s">
         <v>98</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>157</v>
       </c>
       <c r="D62" t="s">
@@ -4640,7 +4614,7 @@
       <c r="B63" t="s">
         <v>97</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D63" t="s">
@@ -4657,7 +4631,7 @@
       <c r="B64" t="s">
         <v>97</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D64" t="s">
@@ -4674,7 +4648,7 @@
       <c r="B65" t="s">
         <v>97</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>159</v>
       </c>
       <c r="D65" t="s">
@@ -4691,7 +4665,7 @@
       <c r="B66" t="s">
         <v>97</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>160</v>
       </c>
       <c r="D66" t="s">
@@ -4708,7 +4682,7 @@
       <c r="B67" t="s">
         <v>97</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>160</v>
       </c>
       <c r="D67" t="s">
@@ -4725,7 +4699,7 @@
       <c r="B68" t="s">
         <v>99</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>161</v>
       </c>
       <c r="D68" t="s">
@@ -4742,7 +4716,7 @@
       <c r="B69" t="s">
         <v>98</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>162</v>
       </c>
       <c r="D69" t="s">
@@ -4759,7 +4733,7 @@
       <c r="B70" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>163</v>
       </c>
       <c r="D70" t="s">
@@ -4776,7 +4750,7 @@
       <c r="B71" t="s">
         <v>97</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D71" t="s">
@@ -4793,7 +4767,7 @@
       <c r="B72" t="s">
         <v>98</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>165</v>
       </c>
       <c r="D72" t="s">
@@ -4810,7 +4784,7 @@
       <c r="B73" t="s">
         <v>98</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>166</v>
       </c>
       <c r="D73" t="s">
@@ -4827,7 +4801,7 @@
       <c r="B74" t="s">
         <v>97</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>167</v>
       </c>
       <c r="D74" t="s">
@@ -4844,7 +4818,7 @@
       <c r="B75" t="s">
         <v>97</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>168</v>
       </c>
       <c r="D75" t="s">
@@ -4861,7 +4835,7 @@
       <c r="B76" t="s">
         <v>99</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>169</v>
       </c>
       <c r="D76" t="s">
@@ -4878,7 +4852,7 @@
       <c r="B77" t="s">
         <v>99</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D77" t="s">
@@ -4895,7 +4869,7 @@
       <c r="B78" t="s">
         <v>99</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>171</v>
       </c>
       <c r="D78" t="s">
@@ -4912,7 +4886,7 @@
       <c r="B79" t="s">
         <v>97</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>172</v>
       </c>
       <c r="D79" t="s">
@@ -4929,7 +4903,7 @@
       <c r="B80" t="s">
         <v>97</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>173</v>
       </c>
       <c r="D80" t="s">
@@ -4946,7 +4920,7 @@
       <c r="B81" t="s">
         <v>98</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>174</v>
       </c>
       <c r="D81" t="s">
@@ -4963,7 +4937,7 @@
       <c r="B82" t="s">
         <v>97</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>175</v>
       </c>
       <c r="D82" t="s">
@@ -4980,7 +4954,7 @@
       <c r="B83" t="s">
         <v>99</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>176</v>
       </c>
       <c r="D83" t="s">
@@ -4997,7 +4971,7 @@
       <c r="B84" t="s">
         <v>98</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>177</v>
       </c>
       <c r="D84" t="s">
@@ -5014,7 +4988,7 @@
       <c r="B85" t="s">
         <v>98</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>178</v>
       </c>
       <c r="D85" t="s">
@@ -5031,7 +5005,7 @@
       <c r="B86" t="s">
         <v>98</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>179</v>
       </c>
       <c r="D86" t="s">
@@ -5048,7 +5022,7 @@
       <c r="B87" t="s">
         <v>97</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>180</v>
       </c>
       <c r="D87" t="s">
@@ -5065,7 +5039,7 @@
       <c r="B88" t="s">
         <v>97</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>181</v>
       </c>
       <c r="D88" t="s">
@@ -5082,7 +5056,7 @@
       <c r="B89" t="s">
         <v>99</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>182</v>
       </c>
       <c r="D89" t="s">
@@ -5099,7 +5073,7 @@
       <c r="B90" t="s">
         <v>97</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>183</v>
       </c>
       <c r="D90" t="s">
@@ -5116,7 +5090,7 @@
       <c r="B91" t="s">
         <v>97</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>184</v>
       </c>
       <c r="D91" t="s">
@@ -5133,7 +5107,7 @@
       <c r="B92" t="s">
         <v>99</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>185</v>
       </c>
       <c r="D92" t="s">
@@ -5150,7 +5124,7 @@
       <c r="B93" t="s">
         <v>98</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D93" t="s">
@@ -5167,7 +5141,7 @@
       <c r="B94" t="s">
         <v>99</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D94" t="s">
@@ -5184,7 +5158,7 @@
       <c r="B95" t="s">
         <v>98</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D95" t="s">
@@ -5201,7 +5175,7 @@
       <c r="B96" t="s">
         <v>99</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>189</v>
       </c>
       <c r="D96" t="s">
@@ -5218,7 +5192,7 @@
       <c r="B97" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D97" t="s">
@@ -5235,7 +5209,7 @@
       <c r="B98" t="s">
         <v>98</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>190</v>
       </c>
       <c r="D98" t="s">
@@ -5252,7 +5226,7 @@
       <c r="B99" t="s">
         <v>99</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>191</v>
       </c>
       <c r="D99" t="s">
@@ -5269,7 +5243,7 @@
       <c r="B100" t="s">
         <v>97</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>192</v>
       </c>
       <c r="D100" t="s">
@@ -5286,7 +5260,7 @@
       <c r="B101" t="s">
         <v>98</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="1" t="s">
         <v>193</v>
       </c>
       <c r="D101" t="s">
@@ -5303,7 +5277,7 @@
       <c r="B102" t="s">
         <v>98</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="1" t="s">
         <v>194</v>
       </c>
       <c r="D102" t="s">
@@ -5320,7 +5294,7 @@
       <c r="B103" t="s">
         <v>97</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="1" t="s">
         <v>192</v>
       </c>
       <c r="D103" t="s">
@@ -5337,7 +5311,7 @@
       <c r="B104" t="s">
         <v>99</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="1" t="s">
         <v>195</v>
       </c>
       <c r="D104" t="s">
@@ -5354,7 +5328,7 @@
       <c r="B105" t="s">
         <v>97</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="1" t="s">
         <v>196</v>
       </c>
       <c r="D105" t="s">
@@ -5371,7 +5345,7 @@
       <c r="B106" t="s">
         <v>97</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="1" t="s">
         <v>197</v>
       </c>
       <c r="D106" t="s">
@@ -5388,7 +5362,7 @@
       <c r="B107" t="s">
         <v>99</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D107" t="s">
@@ -5405,7 +5379,7 @@
       <c r="B108" t="s">
         <v>98</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D108" t="s">
@@ -5422,7 +5396,7 @@
       <c r="B109" t="s">
         <v>98</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D109" t="s">
@@ -5439,7 +5413,7 @@
       <c r="B110" t="s">
         <v>97</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="1" t="s">
         <v>200</v>
       </c>
       <c r="D110" t="s">
@@ -5456,7 +5430,7 @@
       <c r="B111" t="s">
         <v>97</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="1" t="s">
         <v>201</v>
       </c>
       <c r="D111" t="s">
@@ -5473,7 +5447,7 @@
       <c r="B112" t="s">
         <v>99</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="1" t="s">
         <v>202</v>
       </c>
       <c r="D112" t="s">
@@ -5490,7 +5464,7 @@
       <c r="B113" t="s">
         <v>98</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="1" t="s">
         <v>203</v>
       </c>
       <c r="D113" t="s">
@@ -5507,7 +5481,7 @@
       <c r="B114" t="s">
         <v>97</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="1" t="s">
         <v>204</v>
       </c>
       <c r="D114" t="s">
@@ -5524,7 +5498,7 @@
       <c r="B115" t="s">
         <v>99</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>205</v>
       </c>
       <c r="D115" t="s">
@@ -5541,7 +5515,7 @@
       <c r="B116" t="s">
         <v>97</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="1" t="s">
         <v>206</v>
       </c>
       <c r="D116" t="s">
@@ -5558,7 +5532,7 @@
       <c r="B117" t="s">
         <v>98</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="1" t="s">
         <v>207</v>
       </c>
       <c r="D117" t="s">
@@ -5575,7 +5549,7 @@
       <c r="B118" t="s">
         <v>97</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D118" t="s">
@@ -5592,7 +5566,7 @@
       <c r="B119" t="s">
         <v>97</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="1" t="s">
         <v>209</v>
       </c>
       <c r="D119" t="s">
@@ -5609,7 +5583,7 @@
       <c r="B120" t="s">
         <v>99</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="1" t="s">
         <v>210</v>
       </c>
       <c r="D120" t="s">
@@ -5626,7 +5600,7 @@
       <c r="B121" t="s">
         <v>98</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="1" t="s">
         <v>211</v>
       </c>
       <c r="D121" t="s">
@@ -5643,7 +5617,7 @@
       <c r="B122" t="s">
         <v>99</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="1" t="s">
         <v>212</v>
       </c>
       <c r="D122" t="s">
@@ -5660,7 +5634,7 @@
       <c r="B123" t="s">
         <v>98</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="1" t="s">
         <v>213</v>
       </c>
       <c r="D123" t="s">
@@ -5677,7 +5651,7 @@
       <c r="B124" t="s">
         <v>99</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="1" t="s">
         <v>214</v>
       </c>
       <c r="D124" t="s">
@@ -5694,7 +5668,7 @@
       <c r="B125" t="s">
         <v>99</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="1" t="s">
         <v>215</v>
       </c>
       <c r="D125" t="s">
@@ -5711,7 +5685,7 @@
       <c r="B126" t="s">
         <v>99</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="1" t="s">
         <v>215</v>
       </c>
       <c r="D126" t="s">
@@ -5728,7 +5702,7 @@
       <c r="B127" t="s">
         <v>97</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="1" t="s">
         <v>216</v>
       </c>
       <c r="D127" t="s">
@@ -5745,7 +5719,7 @@
       <c r="B128" t="s">
         <v>97</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="1" t="s">
         <v>216</v>
       </c>
       <c r="D128" t="s">
@@ -5762,7 +5736,7 @@
       <c r="B129" t="s">
         <v>98</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="1" t="s">
         <v>217</v>
       </c>
       <c r="D129" t="s">
@@ -5779,7 +5753,7 @@
       <c r="B130" t="s">
         <v>97</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="1" t="s">
         <v>218</v>
       </c>
       <c r="D130" t="s">
@@ -5796,7 +5770,7 @@
       <c r="B131" t="s">
         <v>99</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="1" t="s">
         <v>219</v>
       </c>
       <c r="D131" t="s">
@@ -5813,7 +5787,7 @@
       <c r="B132" t="s">
         <v>99</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D132" t="s">
@@ -5830,7 +5804,7 @@
       <c r="B133" t="s">
         <v>99</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D133" t="s">
@@ -5847,7 +5821,7 @@
       <c r="B134" t="s">
         <v>97</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="1" t="s">
         <v>221</v>
       </c>
       <c r="D134" t="s">
@@ -5864,7 +5838,7 @@
       <c r="B135" t="s">
         <v>99</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="1" t="s">
         <v>222</v>
       </c>
       <c r="D135" t="s">
@@ -5881,7 +5855,7 @@
       <c r="B136" t="s">
         <v>99</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D136" t="s">
@@ -5898,7 +5872,7 @@
       <c r="B137" t="s">
         <v>98</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="1" t="s">
         <v>224</v>
       </c>
       <c r="D137" t="s">
@@ -5915,7 +5889,7 @@
       <c r="B138" t="s">
         <v>98</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="1" t="s">
         <v>225</v>
       </c>
       <c r="D138" t="s">
@@ -5932,7 +5906,7 @@
       <c r="B139" t="s">
         <v>97</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="1" t="s">
         <v>226</v>
       </c>
       <c r="D139" t="s">
@@ -5949,7 +5923,7 @@
       <c r="B140" t="s">
         <v>97</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="1" t="s">
         <v>227</v>
       </c>
       <c r="D140" t="s">
@@ -5966,7 +5940,7 @@
       <c r="B141" t="s">
         <v>98</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="1" t="s">
         <v>228</v>
       </c>
       <c r="D141" t="s">
@@ -5983,7 +5957,7 @@
       <c r="B142" t="s">
         <v>99</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="1" t="s">
         <v>229</v>
       </c>
       <c r="D142" t="s">
@@ -6000,7 +5974,7 @@
       <c r="B143" t="s">
         <v>98</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="1" t="s">
         <v>230</v>
       </c>
       <c r="D143" t="s">
@@ -6017,7 +5991,7 @@
       <c r="B144" t="s">
         <v>99</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="1" t="s">
         <v>231</v>
       </c>
       <c r="D144" t="s">
@@ -6034,7 +6008,7 @@
       <c r="B145" t="s">
         <v>98</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="1" t="s">
         <v>232</v>
       </c>
       <c r="D145" t="s">
@@ -6051,7 +6025,7 @@
       <c r="B146" t="s">
         <v>97</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="1" t="s">
         <v>233</v>
       </c>
       <c r="D146" t="s">
@@ -6068,7 +6042,7 @@
       <c r="B147" t="s">
         <v>98</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="1" t="s">
         <v>234</v>
       </c>
       <c r="D147" t="s">
@@ -6085,7 +6059,7 @@
       <c r="B148" t="s">
         <v>97</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="1" t="s">
         <v>235</v>
       </c>
       <c r="D148" t="s">
@@ -6102,7 +6076,7 @@
       <c r="B149" t="s">
         <v>97</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D149" t="s">
@@ -6119,7 +6093,7 @@
       <c r="B150" t="s">
         <v>97</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D150" t="s">
@@ -6136,7 +6110,7 @@
       <c r="B151" t="s">
         <v>99</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="1" t="s">
         <v>238</v>
       </c>
       <c r="D151" t="s">
@@ -6153,7 +6127,7 @@
       <c r="B152" t="s">
         <v>98</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D152" t="s">
@@ -6170,7 +6144,7 @@
       <c r="B153" t="s">
         <v>97</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D153" t="s">
@@ -6187,7 +6161,7 @@
       <c r="B154" t="s">
         <v>99</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D154" t="s">
@@ -6204,7 +6178,7 @@
       <c r="B155" t="s">
         <v>99</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="1" t="s">
         <v>242</v>
       </c>
       <c r="D155" t="s">
@@ -6221,7 +6195,7 @@
       <c r="B156" t="s">
         <v>98</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D156" t="s">
@@ -6238,7 +6212,7 @@
       <c r="B157" t="s">
         <v>97</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D157" t="s">
@@ -6255,7 +6229,7 @@
       <c r="B158" t="s">
         <v>97</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="1" t="s">
         <v>245</v>
       </c>
       <c r="D158" t="s">
@@ -6272,7 +6246,7 @@
       <c r="B159" t="s">
         <v>97</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D159" t="s">
@@ -6289,7 +6263,7 @@
       <c r="B160" t="s">
         <v>99</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D160" t="s">
@@ -6306,7 +6280,7 @@
       <c r="B161" t="s">
         <v>99</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D161" t="s">
@@ -6323,7 +6297,7 @@
       <c r="B162" t="s">
         <v>97</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D162" t="s">
@@ -6340,7 +6314,7 @@
       <c r="B163" t="s">
         <v>98</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C163" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D163" t="s">
@@ -6357,7 +6331,7 @@
       <c r="B164" t="s">
         <v>98</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C164" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D164" t="s">
@@ -6374,7 +6348,7 @@
       <c r="B165" t="s">
         <v>97</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C165" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D165" t="s">
@@ -6391,7 +6365,7 @@
       <c r="B166" t="s">
         <v>97</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C166" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D166" t="s">
@@ -6408,7 +6382,7 @@
       <c r="B167" t="s">
         <v>98</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C167" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D167" t="s">
@@ -6425,7 +6399,7 @@
       <c r="B168" t="s">
         <v>98</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="C168" s="1" t="s">
         <v>254</v>
       </c>
       <c r="D168" t="s">
@@ -6442,7 +6416,7 @@
       <c r="B169" t="s">
         <v>99</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="C169" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D169" t="s">
@@ -6459,7 +6433,7 @@
       <c r="B170" t="s">
         <v>98</v>
       </c>
-      <c r="C170" s="2" t="s">
+      <c r="C170" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D170" t="s">
@@ -6476,7 +6450,7 @@
       <c r="B171" t="s">
         <v>99</v>
       </c>
-      <c r="C171" s="2" t="s">
+      <c r="C171" s="1" t="s">
         <v>257</v>
       </c>
       <c r="D171" t="s">
@@ -6493,7 +6467,7 @@
       <c r="B172" t="s">
         <v>98</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="C172" s="1" t="s">
         <v>258</v>
       </c>
       <c r="D172" t="s">
@@ -6510,7 +6484,7 @@
       <c r="B173" t="s">
         <v>97</v>
       </c>
-      <c r="C173" s="2" t="s">
+      <c r="C173" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D173" t="s">
@@ -6527,7 +6501,7 @@
       <c r="B174" t="s">
         <v>99</v>
       </c>
-      <c r="C174" s="2" t="s">
+      <c r="C174" s="1" t="s">
         <v>260</v>
       </c>
       <c r="D174" t="s">
@@ -6544,7 +6518,7 @@
       <c r="B175" t="s">
         <v>98</v>
       </c>
-      <c r="C175" s="2" t="s">
+      <c r="C175" s="1" t="s">
         <v>261</v>
       </c>
       <c r="D175" t="s">
@@ -6561,7 +6535,7 @@
       <c r="B176" t="s">
         <v>98</v>
       </c>
-      <c r="C176" s="2" t="s">
+      <c r="C176" s="1" t="s">
         <v>262</v>
       </c>
       <c r="D176" t="s">
@@ -6578,7 +6552,7 @@
       <c r="B177" t="s">
         <v>99</v>
       </c>
-      <c r="C177" s="2" t="s">
+      <c r="C177" s="1" t="s">
         <v>263</v>
       </c>
       <c r="D177" t="s">
@@ -6595,7 +6569,7 @@
       <c r="B178" t="s">
         <v>97</v>
       </c>
-      <c r="C178" s="2" t="s">
+      <c r="C178" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D178" t="s">
@@ -6612,7 +6586,7 @@
       <c r="B179" t="s">
         <v>99</v>
       </c>
-      <c r="C179" s="2" t="s">
+      <c r="C179" s="1" t="s">
         <v>265</v>
       </c>
       <c r="D179" t="s">
@@ -6629,7 +6603,7 @@
       <c r="B180" t="s">
         <v>99</v>
       </c>
-      <c r="C180" s="2" t="s">
+      <c r="C180" s="1" t="s">
         <v>266</v>
       </c>
       <c r="D180" t="s">
@@ -6646,7 +6620,7 @@
       <c r="B181" t="s">
         <v>98</v>
       </c>
-      <c r="C181" s="2" t="s">
+      <c r="C181" s="1" t="s">
         <v>267</v>
       </c>
       <c r="D181" t="s">
@@ -6663,7 +6637,7 @@
       <c r="B182" t="s">
         <v>98</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="C182" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D182" t="s">
@@ -6680,7 +6654,7 @@
       <c r="B183" t="s">
         <v>98</v>
       </c>
-      <c r="C183" s="2" t="s">
+      <c r="C183" s="1" t="s">
         <v>269</v>
       </c>
       <c r="D183" t="s">
@@ -6697,7 +6671,7 @@
       <c r="B184" t="s">
         <v>99</v>
       </c>
-      <c r="C184" s="2" t="s">
+      <c r="C184" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D184" t="s">
@@ -6714,7 +6688,7 @@
       <c r="B185" t="s">
         <v>99</v>
       </c>
-      <c r="C185" s="2" t="s">
+      <c r="C185" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D185" t="s">
@@ -6731,7 +6705,7 @@
       <c r="B186" t="s">
         <v>98</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="C186" s="1" t="s">
         <v>271</v>
       </c>
       <c r="D186" t="s">
@@ -6748,7 +6722,7 @@
       <c r="B187" t="s">
         <v>98</v>
       </c>
-      <c r="C187" s="2" t="s">
+      <c r="C187" s="1" t="s">
         <v>272</v>
       </c>
       <c r="D187" t="s">
@@ -6765,7 +6739,7 @@
       <c r="B188" t="s">
         <v>99</v>
       </c>
-      <c r="C188" s="2" t="s">
+      <c r="C188" s="1" t="s">
         <v>273</v>
       </c>
       <c r="D188" t="s">
@@ -6782,7 +6756,7 @@
       <c r="B189" t="s">
         <v>97</v>
       </c>
-      <c r="C189" s="2" t="s">
+      <c r="C189" s="1" t="s">
         <v>274</v>
       </c>
       <c r="D189" t="s">
@@ -6799,7 +6773,7 @@
       <c r="B190" t="s">
         <v>97</v>
       </c>
-      <c r="C190" s="2" t="s">
+      <c r="C190" s="1" t="s">
         <v>275</v>
       </c>
       <c r="D190" t="s">
@@ -6816,7 +6790,7 @@
       <c r="B191" t="s">
         <v>99</v>
       </c>
-      <c r="C191" s="2" t="s">
+      <c r="C191" s="1" t="s">
         <v>276</v>
       </c>
       <c r="D191" t="s">
@@ -6833,7 +6807,7 @@
       <c r="B192" t="s">
         <v>99</v>
       </c>
-      <c r="C192" s="2" t="s">
+      <c r="C192" s="1" t="s">
         <v>276</v>
       </c>
       <c r="D192" t="s">
@@ -6850,7 +6824,7 @@
       <c r="B193" t="s">
         <v>97</v>
       </c>
-      <c r="C193" s="2" t="s">
+      <c r="C193" s="1" t="s">
         <v>277</v>
       </c>
       <c r="D193" t="s">
@@ -6867,7 +6841,7 @@
       <c r="B194" t="s">
         <v>98</v>
       </c>
-      <c r="C194" s="2" t="s">
+      <c r="C194" s="1" t="s">
         <v>278</v>
       </c>
       <c r="D194" t="s">
@@ -6884,7 +6858,7 @@
       <c r="B195" t="s">
         <v>98</v>
       </c>
-      <c r="C195" s="2" t="s">
+      <c r="C195" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D195" t="s">
@@ -6901,7 +6875,7 @@
       <c r="B196" t="s">
         <v>98</v>
       </c>
-      <c r="C196" s="2" t="s">
+      <c r="C196" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D196" t="s">
@@ -6918,7 +6892,7 @@
       <c r="B197" t="s">
         <v>97</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="C197" s="1" t="s">
         <v>280</v>
       </c>
       <c r="D197" t="s">
@@ -6935,7 +6909,7 @@
       <c r="B198" t="s">
         <v>98</v>
       </c>
-      <c r="C198" s="2" t="s">
+      <c r="C198" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D198" t="s">
@@ -6952,7 +6926,7 @@
       <c r="B199" t="s">
         <v>98</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C199" s="1" t="s">
         <v>282</v>
       </c>
       <c r="D199" t="s">
@@ -6969,7 +6943,7 @@
       <c r="B200" t="s">
         <v>99</v>
       </c>
-      <c r="C200" s="2" t="s">
+      <c r="C200" s="1" t="s">
         <v>283</v>
       </c>
       <c r="D200" t="s">
@@ -6986,7 +6960,7 @@
       <c r="B201" t="s">
         <v>99</v>
       </c>
-      <c r="C201" s="2" t="s">
+      <c r="C201" s="1" t="s">
         <v>284</v>
       </c>
       <c r="D201" t="s">
@@ -7003,7 +6977,7 @@
       <c r="B202" t="s">
         <v>99</v>
       </c>
-      <c r="C202" s="2" t="s">
+      <c r="C202" s="1" t="s">
         <v>285</v>
       </c>
       <c r="D202" t="s">
@@ -7020,7 +6994,7 @@
       <c r="B203" t="s">
         <v>97</v>
       </c>
-      <c r="C203" s="2" t="s">
+      <c r="C203" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D203" t="s">
@@ -7037,7 +7011,7 @@
       <c r="B204" t="s">
         <v>98</v>
       </c>
-      <c r="C204" s="2" t="s">
+      <c r="C204" s="1" t="s">
         <v>287</v>
       </c>
       <c r="D204" t="s">
@@ -7054,7 +7028,7 @@
       <c r="B205" t="s">
         <v>98</v>
       </c>
-      <c r="C205" s="2" t="s">
+      <c r="C205" s="1" t="s">
         <v>288</v>
       </c>
       <c r="D205" t="s">
@@ -7071,7 +7045,7 @@
       <c r="B206" t="s">
         <v>97</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="C206" s="1" t="s">
         <v>289</v>
       </c>
       <c r="D206" t="s">
@@ -7088,7 +7062,7 @@
       <c r="B207" t="s">
         <v>97</v>
       </c>
-      <c r="C207" s="2" t="s">
+      <c r="C207" s="1" t="s">
         <v>290</v>
       </c>
       <c r="D207" t="s">
@@ -7105,7 +7079,7 @@
       <c r="B208" t="s">
         <v>98</v>
       </c>
-      <c r="C208" s="2" t="s">
+      <c r="C208" s="1" t="s">
         <v>291</v>
       </c>
       <c r="D208" t="s">
@@ -7122,7 +7096,7 @@
       <c r="B209" t="s">
         <v>98</v>
       </c>
-      <c r="C209" s="2" t="s">
+      <c r="C209" s="1" t="s">
         <v>292</v>
       </c>
       <c r="D209" t="s">
@@ -7139,7 +7113,7 @@
       <c r="B210" t="s">
         <v>98</v>
       </c>
-      <c r="C210" s="2" t="s">
+      <c r="C210" s="1" t="s">
         <v>293</v>
       </c>
       <c r="D210" t="s">
@@ -7156,7 +7130,7 @@
       <c r="B211" t="s">
         <v>97</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="C211" s="1" t="s">
         <v>294</v>
       </c>
       <c r="D211" t="s">
@@ -7173,7 +7147,7 @@
       <c r="B212" t="s">
         <v>99</v>
       </c>
-      <c r="C212" s="2" t="s">
+      <c r="C212" s="1" t="s">
         <v>295</v>
       </c>
       <c r="D212" t="s">
@@ -7190,7 +7164,7 @@
       <c r="B213" t="s">
         <v>98</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="C213" s="1" t="s">
         <v>296</v>
       </c>
       <c r="D213" t="s">
@@ -7207,7 +7181,7 @@
       <c r="B214" t="s">
         <v>97</v>
       </c>
-      <c r="C214" s="2" t="s">
+      <c r="C214" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D214" t="s">
@@ -7224,7 +7198,7 @@
       <c r="B215" t="s">
         <v>98</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="C215" s="1" t="s">
         <v>298</v>
       </c>
       <c r="D215" t="s">
@@ -7241,7 +7215,7 @@
       <c r="B216" t="s">
         <v>97</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="C216" s="1" t="s">
         <v>299</v>
       </c>
       <c r="D216" t="s">
@@ -7258,7 +7232,7 @@
       <c r="B217" t="s">
         <v>99</v>
       </c>
-      <c r="C217" s="2" t="s">
+      <c r="C217" s="1" t="s">
         <v>300</v>
       </c>
       <c r="D217" t="s">
@@ -7275,7 +7249,7 @@
       <c r="B218" t="s">
         <v>98</v>
       </c>
-      <c r="C218" s="2" t="s">
+      <c r="C218" s="1" t="s">
         <v>301</v>
       </c>
       <c r="D218" t="s">
@@ -7292,7 +7266,7 @@
       <c r="B219" t="s">
         <v>98</v>
       </c>
-      <c r="C219" s="2" t="s">
+      <c r="C219" s="1" t="s">
         <v>302</v>
       </c>
       <c r="D219" t="s">
@@ -7309,7 +7283,7 @@
       <c r="B220" t="s">
         <v>97</v>
       </c>
-      <c r="C220" s="2" t="s">
+      <c r="C220" s="1" t="s">
         <v>303</v>
       </c>
       <c r="D220" t="s">
@@ -7326,7 +7300,7 @@
       <c r="B221" t="s">
         <v>99</v>
       </c>
-      <c r="C221" s="2" t="s">
+      <c r="C221" s="1" t="s">
         <v>304</v>
       </c>
       <c r="D221" t="s">
@@ -7343,7 +7317,7 @@
       <c r="B222" t="s">
         <v>99</v>
       </c>
-      <c r="C222" s="2" t="s">
+      <c r="C222" s="1" t="s">
         <v>305</v>
       </c>
       <c r="D222" t="s">
@@ -7360,7 +7334,7 @@
       <c r="B223" t="s">
         <v>99</v>
       </c>
-      <c r="C223" s="2" t="s">
+      <c r="C223" s="1" t="s">
         <v>306</v>
       </c>
       <c r="D223" t="s">
@@ -7377,7 +7351,7 @@
       <c r="B224" t="s">
         <v>97</v>
       </c>
-      <c r="C224" s="2" t="s">
+      <c r="C224" s="1" t="s">
         <v>307</v>
       </c>
       <c r="D224" t="s">
@@ -7394,7 +7368,7 @@
       <c r="B225" t="s">
         <v>97</v>
       </c>
-      <c r="C225" s="2" t="s">
+      <c r="C225" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D225" t="s">
@@ -7411,7 +7385,7 @@
       <c r="B226" t="s">
         <v>99</v>
       </c>
-      <c r="C226" s="2" t="s">
+      <c r="C226" s="1" t="s">
         <v>309</v>
       </c>
       <c r="D226" t="s">
@@ -7428,7 +7402,7 @@
       <c r="B227" t="s">
         <v>99</v>
       </c>
-      <c r="C227" s="2" t="s">
+      <c r="C227" s="1" t="s">
         <v>309</v>
       </c>
       <c r="D227" t="s">
@@ -7445,7 +7419,7 @@
       <c r="B228" t="s">
         <v>99</v>
       </c>
-      <c r="C228" s="2" t="s">
+      <c r="C228" s="1" t="s">
         <v>310</v>
       </c>
       <c r="D228" t="s">
@@ -7462,7 +7436,7 @@
       <c r="B229" t="s">
         <v>99</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="C229" s="1" t="s">
         <v>311</v>
       </c>
       <c r="D229" t="s">
@@ -7479,7 +7453,7 @@
       <c r="B230" t="s">
         <v>99</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C230" s="1" t="s">
         <v>311</v>
       </c>
       <c r="D230" t="s">
@@ -7496,7 +7470,7 @@
       <c r="B231" t="s">
         <v>99</v>
       </c>
-      <c r="C231" s="2" t="s">
+      <c r="C231" s="1" t="s">
         <v>312</v>
       </c>
       <c r="D231" t="s">
@@ -7513,7 +7487,7 @@
       <c r="B232" t="s">
         <v>99</v>
       </c>
-      <c r="C232" s="2" t="s">
+      <c r="C232" s="1" t="s">
         <v>313</v>
       </c>
       <c r="D232" t="s">
@@ -7530,7 +7504,7 @@
       <c r="B233" t="s">
         <v>97</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="C233" s="1" t="s">
         <v>314</v>
       </c>
       <c r="D233" t="s">
@@ -7547,7 +7521,7 @@
       <c r="B234" t="s">
         <v>98</v>
       </c>
-      <c r="C234" s="2" t="s">
+      <c r="C234" s="1" t="s">
         <v>315</v>
       </c>
       <c r="D234" t="s">
@@ -7564,7 +7538,7 @@
       <c r="B235" t="s">
         <v>99</v>
       </c>
-      <c r="C235" s="2" t="s">
+      <c r="C235" s="1" t="s">
         <v>316</v>
       </c>
       <c r="D235" t="s">
@@ -7581,7 +7555,7 @@
       <c r="B236" t="s">
         <v>97</v>
       </c>
-      <c r="C236" s="2" t="s">
+      <c r="C236" s="1" t="s">
         <v>317</v>
       </c>
       <c r="D236" t="s">
@@ -7598,7 +7572,7 @@
       <c r="B237" t="s">
         <v>99</v>
       </c>
-      <c r="C237" s="2" t="s">
+      <c r="C237" s="1" t="s">
         <v>318</v>
       </c>
       <c r="D237" t="s">
@@ -7615,7 +7589,7 @@
       <c r="B238" t="s">
         <v>99</v>
       </c>
-      <c r="C238" s="2" t="s">
+      <c r="C238" s="1" t="s">
         <v>319</v>
       </c>
       <c r="D238" t="s">
@@ -7632,7 +7606,7 @@
       <c r="B239" t="s">
         <v>98</v>
       </c>
-      <c r="C239" s="2" t="s">
+      <c r="C239" s="1" t="s">
         <v>320</v>
       </c>
       <c r="D239" t="s">
@@ -7649,7 +7623,7 @@
       <c r="B240" t="s">
         <v>99</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="C240" s="1" t="s">
         <v>321</v>
       </c>
       <c r="D240" t="s">
@@ -7666,7 +7640,7 @@
       <c r="B241" t="s">
         <v>99</v>
       </c>
-      <c r="C241" s="2" t="s">
+      <c r="C241" s="1" t="s">
         <v>321</v>
       </c>
       <c r="D241" t="s">
@@ -7683,7 +7657,7 @@
       <c r="B242" t="s">
         <v>98</v>
       </c>
-      <c r="C242" s="2" t="s">
+      <c r="C242" s="1" t="s">
         <v>320</v>
       </c>
       <c r="D242" t="s">
@@ -7700,7 +7674,7 @@
       <c r="B243" t="s">
         <v>99</v>
       </c>
-      <c r="C243" s="2" t="s">
+      <c r="C243" s="1" t="s">
         <v>321</v>
       </c>
       <c r="D243" t="s">
@@ -7717,7 +7691,7 @@
       <c r="B244" t="s">
         <v>99</v>
       </c>
-      <c r="C244" s="2" t="s">
+      <c r="C244" s="1" t="s">
         <v>322</v>
       </c>
       <c r="D244" t="s">
@@ -7734,7 +7708,7 @@
       <c r="B245" t="s">
         <v>97</v>
       </c>
-      <c r="C245" s="2" t="s">
+      <c r="C245" s="1" t="s">
         <v>323</v>
       </c>
       <c r="D245" t="s">
@@ -7751,7 +7725,7 @@
       <c r="B246" t="s">
         <v>97</v>
       </c>
-      <c r="C246" s="2" t="s">
+      <c r="C246" s="1" t="s">
         <v>323</v>
       </c>
       <c r="D246" t="s">
@@ -7768,7 +7742,7 @@
       <c r="B247" t="s">
         <v>99</v>
       </c>
-      <c r="C247" s="2" t="s">
+      <c r="C247" s="1" t="s">
         <v>324</v>
       </c>
       <c r="D247" t="s">
@@ -7785,7 +7759,7 @@
       <c r="B248" t="s">
         <v>99</v>
       </c>
-      <c r="C248" s="2" t="s">
+      <c r="C248" s="1" t="s">
         <v>325</v>
       </c>
       <c r="D248" t="s">
@@ -7802,7 +7776,7 @@
       <c r="B249" t="s">
         <v>99</v>
       </c>
-      <c r="C249" s="2" t="s">
+      <c r="C249" s="1" t="s">
         <v>326</v>
       </c>
       <c r="D249" t="s">
@@ -7819,7 +7793,7 @@
       <c r="B250" t="s">
         <v>97</v>
       </c>
-      <c r="C250" s="2" t="s">
+      <c r="C250" s="1" t="s">
         <v>327</v>
       </c>
       <c r="D250" t="s">
@@ -7836,7 +7810,7 @@
       <c r="B251" t="s">
         <v>98</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="C251" s="1" t="s">
         <v>328</v>
       </c>
       <c r="D251" t="s">
@@ -7853,7 +7827,7 @@
       <c r="B252" t="s">
         <v>97</v>
       </c>
-      <c r="C252" s="2" t="s">
+      <c r="C252" s="1" t="s">
         <v>329</v>
       </c>
       <c r="D252" t="s">
@@ -7870,7 +7844,7 @@
       <c r="B253" t="s">
         <v>99</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="C253" s="1" t="s">
         <v>330</v>
       </c>
       <c r="D253" t="s">
@@ -7887,7 +7861,7 @@
       <c r="B254" t="s">
         <v>99</v>
       </c>
-      <c r="C254" s="2" t="s">
+      <c r="C254" s="1" t="s">
         <v>331</v>
       </c>
       <c r="D254" t="s">
@@ -7904,7 +7878,7 @@
       <c r="B255" t="s">
         <v>97</v>
       </c>
-      <c r="C255" s="2" t="s">
+      <c r="C255" s="1" t="s">
         <v>332</v>
       </c>
       <c r="D255" t="s">
@@ -7921,7 +7895,7 @@
       <c r="B256" t="s">
         <v>98</v>
       </c>
-      <c r="C256" s="2" t="s">
+      <c r="C256" s="1" t="s">
         <v>333</v>
       </c>
       <c r="D256" t="s">
@@ -7938,7 +7912,7 @@
       <c r="B257" t="s">
         <v>97</v>
       </c>
-      <c r="C257" s="2" t="s">
+      <c r="C257" s="1" t="s">
         <v>334</v>
       </c>
       <c r="D257" t="s">
@@ -7955,7 +7929,7 @@
       <c r="B258" t="s">
         <v>97</v>
       </c>
-      <c r="C258" s="2" t="s">
+      <c r="C258" s="1" t="s">
         <v>335</v>
       </c>
       <c r="D258" t="s">
@@ -7972,7 +7946,7 @@
       <c r="B259" t="s">
         <v>97</v>
       </c>
-      <c r="C259" s="2" t="s">
+      <c r="C259" s="1" t="s">
         <v>334</v>
       </c>
       <c r="D259" t="s">
@@ -7989,7 +7963,7 @@
       <c r="B260" t="s">
         <v>97</v>
       </c>
-      <c r="C260" s="2" t="s">
+      <c r="C260" s="1" t="s">
         <v>336</v>
       </c>
       <c r="D260" t="s">
@@ -8006,7 +7980,7 @@
       <c r="B261" t="s">
         <v>98</v>
       </c>
-      <c r="C261" s="2" t="s">
+      <c r="C261" s="1" t="s">
         <v>337</v>
       </c>
       <c r="D261" t="s">
@@ -8023,7 +7997,7 @@
       <c r="B262" t="s">
         <v>99</v>
       </c>
-      <c r="C262" s="2" t="s">
+      <c r="C262" s="1" t="s">
         <v>338</v>
       </c>
       <c r="D262" t="s">
@@ -8040,7 +8014,7 @@
       <c r="B263" t="s">
         <v>98</v>
       </c>
-      <c r="C263" s="2" t="s">
+      <c r="C263" s="1" t="s">
         <v>339</v>
       </c>
       <c r="D263" t="s">
@@ -8057,7 +8031,7 @@
       <c r="B264" t="s">
         <v>97</v>
       </c>
-      <c r="C264" s="2" t="s">
+      <c r="C264" s="1" t="s">
         <v>340</v>
       </c>
       <c r="D264" t="s">
@@ -8074,7 +8048,7 @@
       <c r="B265" t="s">
         <v>98</v>
       </c>
-      <c r="C265" s="2" t="s">
+      <c r="C265" s="1" t="s">
         <v>339</v>
       </c>
       <c r="D265" t="s">
@@ -8091,7 +8065,7 @@
       <c r="B266" t="s">
         <v>98</v>
       </c>
-      <c r="C266" s="2" t="s">
+      <c r="C266" s="1" t="s">
         <v>341</v>
       </c>
       <c r="D266" t="s">
@@ -8108,7 +8082,7 @@
       <c r="B267" t="s">
         <v>99</v>
       </c>
-      <c r="C267" s="2" t="s">
+      <c r="C267" s="1" t="s">
         <v>342</v>
       </c>
       <c r="D267" t="s">
@@ -8125,7 +8099,7 @@
       <c r="B268" t="s">
         <v>98</v>
       </c>
-      <c r="C268" s="2" t="s">
+      <c r="C268" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D268" t="s">
@@ -8142,7 +8116,7 @@
       <c r="B269" t="s">
         <v>99</v>
       </c>
-      <c r="C269" s="2" t="s">
+      <c r="C269" s="1" t="s">
         <v>344</v>
       </c>
       <c r="D269" t="s">
@@ -8159,7 +8133,7 @@
       <c r="B270" t="s">
         <v>99</v>
       </c>
-      <c r="C270" s="2" t="s">
+      <c r="C270" s="1" t="s">
         <v>345</v>
       </c>
       <c r="D270" t="s">
@@ -8176,7 +8150,7 @@
       <c r="B271" t="s">
         <v>99</v>
       </c>
-      <c r="C271" s="2" t="s">
+      <c r="C271" s="1" t="s">
         <v>342</v>
       </c>
       <c r="D271" t="s">
@@ -8193,7 +8167,7 @@
       <c r="B272" t="s">
         <v>97</v>
       </c>
-      <c r="C272" s="2" t="s">
+      <c r="C272" s="1" t="s">
         <v>346</v>
       </c>
       <c r="D272" t="s">
@@ -8210,7 +8184,7 @@
       <c r="B273" t="s">
         <v>99</v>
       </c>
-      <c r="C273" s="2" t="s">
+      <c r="C273" s="1" t="s">
         <v>347</v>
       </c>
       <c r="D273" t="s">
@@ -8227,7 +8201,7 @@
       <c r="B274" t="s">
         <v>97</v>
       </c>
-      <c r="C274" s="2" t="s">
+      <c r="C274" s="1" t="s">
         <v>348</v>
       </c>
       <c r="D274" t="s">
@@ -8244,7 +8218,7 @@
       <c r="B275" t="s">
         <v>97</v>
       </c>
-      <c r="C275" s="2" t="s">
+      <c r="C275" s="1" t="s">
         <v>349</v>
       </c>
       <c r="D275" t="s">
@@ -8261,7 +8235,7 @@
       <c r="B276" t="s">
         <v>98</v>
       </c>
-      <c r="C276" s="2" t="s">
+      <c r="C276" s="1" t="s">
         <v>350</v>
       </c>
       <c r="D276" t="s">
@@ -8278,7 +8252,7 @@
       <c r="B277" t="s">
         <v>99</v>
       </c>
-      <c r="C277" s="2" t="s">
+      <c r="C277" s="1" t="s">
         <v>351</v>
       </c>
       <c r="D277" t="s">
@@ -8295,7 +8269,7 @@
       <c r="B278" t="s">
         <v>97</v>
       </c>
-      <c r="C278" s="2" t="s">
+      <c r="C278" s="1" t="s">
         <v>352</v>
       </c>
       <c r="D278" t="s">
@@ -8312,7 +8286,7 @@
       <c r="B279" t="s">
         <v>97</v>
       </c>
-      <c r="C279" s="2" t="s">
+      <c r="C279" s="1" t="s">
         <v>353</v>
       </c>
       <c r="D279" t="s">
@@ -8329,7 +8303,7 @@
       <c r="B280" t="s">
         <v>99</v>
       </c>
-      <c r="C280" s="2" t="s">
+      <c r="C280" s="1" t="s">
         <v>354</v>
       </c>
       <c r="D280" t="s">
@@ -8346,7 +8320,7 @@
       <c r="B281" t="s">
         <v>99</v>
       </c>
-      <c r="C281" s="2" t="s">
+      <c r="C281" s="1" t="s">
         <v>355</v>
       </c>
       <c r="D281" t="s">
@@ -8363,7 +8337,7 @@
       <c r="B282" t="s">
         <v>99</v>
       </c>
-      <c r="C282" s="2" t="s">
+      <c r="C282" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D282" t="s">
@@ -8380,7 +8354,7 @@
       <c r="B283" t="s">
         <v>99</v>
       </c>
-      <c r="C283" s="2" t="s">
+      <c r="C283" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D283" t="s">
@@ -8397,7 +8371,7 @@
       <c r="B284" t="s">
         <v>97</v>
       </c>
-      <c r="C284" s="2" t="s">
+      <c r="C284" s="1" t="s">
         <v>357</v>
       </c>
       <c r="D284" t="s">
@@ -8414,7 +8388,7 @@
       <c r="B285" t="s">
         <v>99</v>
       </c>
-      <c r="C285" s="2" t="s">
+      <c r="C285" s="1" t="s">
         <v>358</v>
       </c>
       <c r="D285" t="s">
@@ -8431,7 +8405,7 @@
       <c r="B286" t="s">
         <v>99</v>
       </c>
-      <c r="C286" s="2" t="s">
+      <c r="C286" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D286" t="s">
@@ -8448,7 +8422,7 @@
       <c r="B287" t="s">
         <v>97</v>
       </c>
-      <c r="C287" s="2" t="s">
+      <c r="C287" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D287" t="s">
@@ -8465,7 +8439,7 @@
       <c r="B288" t="s">
         <v>99</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="C288" s="1" t="s">
         <v>361</v>
       </c>
       <c r="D288" t="s">
@@ -8482,7 +8456,7 @@
       <c r="B289" t="s">
         <v>97</v>
       </c>
-      <c r="C289" s="2" t="s">
+      <c r="C289" s="1" t="s">
         <v>362</v>
       </c>
       <c r="D289" t="s">
@@ -8499,7 +8473,7 @@
       <c r="B290" t="s">
         <v>97</v>
       </c>
-      <c r="C290" s="2" t="s">
+      <c r="C290" s="1" t="s">
         <v>363</v>
       </c>
       <c r="D290" t="s">
@@ -8516,7 +8490,7 @@
       <c r="B291" t="s">
         <v>99</v>
       </c>
-      <c r="C291" s="2" t="s">
+      <c r="C291" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D291" t="s">
@@ -8533,7 +8507,7 @@
       <c r="B292" t="s">
         <v>97</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="C292" s="1" t="s">
         <v>365</v>
       </c>
       <c r="D292" t="s">
@@ -8550,7 +8524,7 @@
       <c r="B293" t="s">
         <v>97</v>
       </c>
-      <c r="C293" s="2" t="s">
+      <c r="C293" s="1" t="s">
         <v>366</v>
       </c>
       <c r="D293" t="s">
@@ -8567,7 +8541,7 @@
       <c r="B294" t="s">
         <v>99</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="C294" s="1" t="s">
         <v>367</v>
       </c>
       <c r="D294" t="s">
@@ -8584,7 +8558,7 @@
       <c r="B295" t="s">
         <v>98</v>
       </c>
-      <c r="C295" s="2" t="s">
+      <c r="C295" s="1" t="s">
         <v>368</v>
       </c>
       <c r="D295" t="s">
@@ -8601,7 +8575,7 @@
       <c r="B296" t="s">
         <v>98</v>
       </c>
-      <c r="C296" s="2" t="s">
+      <c r="C296" s="1" t="s">
         <v>369</v>
       </c>
       <c r="D296" t="s">
@@ -8618,7 +8592,7 @@
       <c r="B297" t="s">
         <v>98</v>
       </c>
-      <c r="C297" s="2" t="s">
+      <c r="C297" s="1" t="s">
         <v>369</v>
       </c>
       <c r="D297" t="s">
@@ -8635,7 +8609,7 @@
       <c r="B298" t="s">
         <v>98</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="C298" s="1" t="s">
         <v>370</v>
       </c>
       <c r="D298" t="s">
@@ -8652,7 +8626,7 @@
       <c r="B299" t="s">
         <v>97</v>
       </c>
-      <c r="C299" s="2" t="s">
+      <c r="C299" s="1" t="s">
         <v>371</v>
       </c>
       <c r="D299" t="s">
@@ -8669,7 +8643,7 @@
       <c r="B300" t="s">
         <v>98</v>
       </c>
-      <c r="C300" s="2" t="s">
+      <c r="C300" s="1" t="s">
         <v>370</v>
       </c>
       <c r="D300" t="s">
@@ -8686,7 +8660,7 @@
       <c r="B301" t="s">
         <v>97</v>
       </c>
-      <c r="C301" s="2" t="s">
+      <c r="C301" s="1" t="s">
         <v>372</v>
       </c>
       <c r="D301" t="s">
@@ -8703,7 +8677,7 @@
       <c r="B302" t="s">
         <v>98</v>
       </c>
-      <c r="C302" s="2" t="s">
+      <c r="C302" s="1" t="s">
         <v>373</v>
       </c>
       <c r="D302" t="s">
@@ -8720,7 +8694,7 @@
       <c r="B303" t="s">
         <v>97</v>
       </c>
-      <c r="C303" s="2" t="s">
+      <c r="C303" s="1" t="s">
         <v>374</v>
       </c>
       <c r="D303" t="s">
@@ -8737,7 +8711,7 @@
       <c r="B304" t="s">
         <v>97</v>
       </c>
-      <c r="C304" s="2" t="s">
+      <c r="C304" s="1" t="s">
         <v>375</v>
       </c>
       <c r="D304" t="s">
@@ -8754,7 +8728,7 @@
       <c r="B305" t="s">
         <v>97</v>
       </c>
-      <c r="C305" s="2" t="s">
+      <c r="C305" s="1" t="s">
         <v>374</v>
       </c>
       <c r="D305" t="s">
@@ -8771,7 +8745,7 @@
       <c r="B306" t="s">
         <v>97</v>
       </c>
-      <c r="C306" s="2" t="s">
+      <c r="C306" s="1" t="s">
         <v>376</v>
       </c>
       <c r="D306" t="s">
@@ -8788,7 +8762,7 @@
       <c r="B307" t="s">
         <v>98</v>
       </c>
-      <c r="C307" s="2" t="s">
+      <c r="C307" s="1" t="s">
         <v>377</v>
       </c>
       <c r="D307" t="s">
@@ -8805,7 +8779,7 @@
       <c r="B308" t="s">
         <v>99</v>
       </c>
-      <c r="C308" s="2" t="s">
+      <c r="C308" s="1" t="s">
         <v>378</v>
       </c>
       <c r="D308" t="s">
@@ -8822,7 +8796,7 @@
       <c r="B309" t="s">
         <v>99</v>
       </c>
-      <c r="C309" s="2" t="s">
+      <c r="C309" s="1" t="s">
         <v>378</v>
       </c>
       <c r="D309" t="s">
@@ -8839,7 +8813,7 @@
       <c r="B310" t="s">
         <v>99</v>
       </c>
-      <c r="C310" s="2" t="s">
+      <c r="C310" s="1" t="s">
         <v>379</v>
       </c>
       <c r="D310" t="s">
@@ -8856,7 +8830,7 @@
       <c r="B311" t="s">
         <v>98</v>
       </c>
-      <c r="C311" s="2" t="s">
+      <c r="C311" s="1" t="s">
         <v>380</v>
       </c>
       <c r="D311" t="s">
@@ -8873,7 +8847,7 @@
       <c r="B312" t="s">
         <v>99</v>
       </c>
-      <c r="C312" s="2" t="s">
+      <c r="C312" s="1" t="s">
         <v>381</v>
       </c>
       <c r="D312" t="s">
@@ -8890,7 +8864,7 @@
       <c r="B313" t="s">
         <v>99</v>
       </c>
-      <c r="C313" s="2" t="s">
+      <c r="C313" s="1" t="s">
         <v>382</v>
       </c>
       <c r="D313" t="s">
@@ -8907,7 +8881,7 @@
       <c r="B314" t="s">
         <v>99</v>
       </c>
-      <c r="C314" s="2" t="s">
+      <c r="C314" s="1" t="s">
         <v>383</v>
       </c>
       <c r="D314" t="s">
@@ -8924,7 +8898,7 @@
       <c r="B315" t="s">
         <v>99</v>
       </c>
-      <c r="C315" s="2" t="s">
+      <c r="C315" s="1" t="s">
         <v>383</v>
       </c>
       <c r="D315" t="s">
@@ -8941,7 +8915,7 @@
       <c r="B316" t="s">
         <v>99</v>
       </c>
-      <c r="C316" s="2" t="s">
+      <c r="C316" s="1" t="s">
         <v>384</v>
       </c>
       <c r="D316" t="s">
@@ -8958,7 +8932,7 @@
       <c r="B317" t="s">
         <v>98</v>
       </c>
-      <c r="C317" s="2" t="s">
+      <c r="C317" s="1" t="s">
         <v>385</v>
       </c>
       <c r="D317" t="s">
@@ -8975,7 +8949,7 @@
       <c r="B318" t="s">
         <v>99</v>
       </c>
-      <c r="C318" s="2" t="s">
+      <c r="C318" s="1" t="s">
         <v>386</v>
       </c>
       <c r="D318" t="s">
@@ -8992,7 +8966,7 @@
       <c r="B319" t="s">
         <v>99</v>
       </c>
-      <c r="C319" s="2" t="s">
+      <c r="C319" s="1" t="s">
         <v>387</v>
       </c>
       <c r="D319" t="s">
@@ -9009,7 +8983,7 @@
       <c r="B320" t="s">
         <v>97</v>
       </c>
-      <c r="C320" s="2" t="s">
+      <c r="C320" s="1" t="s">
         <v>388</v>
       </c>
       <c r="D320" t="s">
@@ -9026,7 +9000,7 @@
       <c r="B321" t="s">
         <v>97</v>
       </c>
-      <c r="C321" s="2" t="s">
+      <c r="C321" s="1" t="s">
         <v>389</v>
       </c>
       <c r="D321" t="s">
@@ -9043,7 +9017,7 @@
       <c r="B322" t="s">
         <v>97</v>
       </c>
-      <c r="C322" s="2" t="s">
+      <c r="C322" s="1" t="s">
         <v>390</v>
       </c>
       <c r="D322" t="s">
@@ -9060,7 +9034,7 @@
       <c r="B323" t="s">
         <v>99</v>
       </c>
-      <c r="C323" s="2" t="s">
+      <c r="C323" s="1" t="s">
         <v>391</v>
       </c>
       <c r="D323" t="s">
@@ -9077,7 +9051,7 @@
       <c r="B324" t="s">
         <v>98</v>
       </c>
-      <c r="C324" s="2" t="s">
+      <c r="C324" s="1" t="s">
         <v>392</v>
       </c>
       <c r="D324" t="s">
@@ -9094,7 +9068,7 @@
       <c r="B325" t="s">
         <v>98</v>
       </c>
-      <c r="C325" s="2" t="s">
+      <c r="C325" s="1" t="s">
         <v>393</v>
       </c>
       <c r="D325" t="s">
@@ -9111,7 +9085,7 @@
       <c r="B326" t="s">
         <v>99</v>
       </c>
-      <c r="C326" s="2" t="s">
+      <c r="C326" s="1" t="s">
         <v>394</v>
       </c>
       <c r="D326" t="s">
@@ -9128,7 +9102,7 @@
       <c r="B327" t="s">
         <v>99</v>
       </c>
-      <c r="C327" s="2" t="s">
+      <c r="C327" s="1" t="s">
         <v>395</v>
       </c>
       <c r="D327" t="s">
@@ -9145,7 +9119,7 @@
       <c r="B328" t="s">
         <v>98</v>
       </c>
-      <c r="C328" s="2" t="s">
+      <c r="C328" s="1" t="s">
         <v>396</v>
       </c>
       <c r="D328" t="s">
@@ -9162,7 +9136,7 @@
       <c r="B329" t="s">
         <v>99</v>
       </c>
-      <c r="C329" s="2" t="s">
+      <c r="C329" s="1" t="s">
         <v>397</v>
       </c>
       <c r="D329" t="s">
@@ -9179,7 +9153,7 @@
       <c r="B330" t="s">
         <v>97</v>
       </c>
-      <c r="C330" s="2" t="s">
+      <c r="C330" s="1" t="s">
         <v>398</v>
       </c>
       <c r="D330" t="s">
@@ -9196,7 +9170,7 @@
       <c r="B331" t="s">
         <v>98</v>
       </c>
-      <c r="C331" s="2" t="s">
+      <c r="C331" s="1" t="s">
         <v>399</v>
       </c>
       <c r="D331" t="s">
@@ -9213,7 +9187,7 @@
       <c r="B332" t="s">
         <v>99</v>
       </c>
-      <c r="C332" s="2" t="s">
+      <c r="C332" s="1" t="s">
         <v>400</v>
       </c>
       <c r="D332" t="s">
@@ -9230,7 +9204,7 @@
       <c r="B333" t="s">
         <v>97</v>
       </c>
-      <c r="C333" s="2" t="s">
+      <c r="C333" s="1" t="s">
         <v>401</v>
       </c>
       <c r="D333" t="s">
@@ -9247,7 +9221,7 @@
       <c r="B334" t="s">
         <v>97</v>
       </c>
-      <c r="C334" s="2" t="s">
+      <c r="C334" s="1" t="s">
         <v>402</v>
       </c>
       <c r="D334" t="s">
@@ -9264,7 +9238,7 @@
       <c r="B335" t="s">
         <v>98</v>
       </c>
-      <c r="C335" s="2" t="s">
+      <c r="C335" s="1" t="s">
         <v>403</v>
       </c>
       <c r="D335" t="s">
@@ -9281,7 +9255,7 @@
       <c r="B336" t="s">
         <v>97</v>
       </c>
-      <c r="C336" s="2" t="s">
+      <c r="C336" s="1" t="s">
         <v>404</v>
       </c>
       <c r="D336" t="s">
@@ -9298,7 +9272,7 @@
       <c r="B337" t="s">
         <v>98</v>
       </c>
-      <c r="C337" s="2" t="s">
+      <c r="C337" s="1" t="s">
         <v>405</v>
       </c>
       <c r="D337" t="s">
@@ -9315,7 +9289,7 @@
       <c r="B338" t="s">
         <v>97</v>
       </c>
-      <c r="C338" s="2" t="s">
+      <c r="C338" s="1" t="s">
         <v>406</v>
       </c>
       <c r="D338" t="s">
@@ -9332,7 +9306,7 @@
       <c r="B339" t="s">
         <v>99</v>
       </c>
-      <c r="C339" s="2" t="s">
+      <c r="C339" s="1" t="s">
         <v>407</v>
       </c>
       <c r="D339" t="s">
@@ -9349,7 +9323,7 @@
       <c r="B340" t="s">
         <v>99</v>
       </c>
-      <c r="C340" s="2" t="s">
+      <c r="C340" s="1" t="s">
         <v>408</v>
       </c>
       <c r="D340" t="s">
@@ -9366,7 +9340,7 @@
       <c r="B341" t="s">
         <v>98</v>
       </c>
-      <c r="C341" s="2" t="s">
+      <c r="C341" s="1" t="s">
         <v>409</v>
       </c>
       <c r="D341" t="s">
@@ -9383,7 +9357,7 @@
       <c r="B342" t="s">
         <v>97</v>
       </c>
-      <c r="C342" s="2" t="s">
+      <c r="C342" s="1" t="s">
         <v>410</v>
       </c>
       <c r="D342" t="s">
@@ -9400,7 +9374,7 @@
       <c r="B343" t="s">
         <v>99</v>
       </c>
-      <c r="C343" s="2" t="s">
+      <c r="C343" s="1" t="s">
         <v>411</v>
       </c>
       <c r="D343" t="s">
@@ -9417,7 +9391,7 @@
       <c r="B344" t="s">
         <v>97</v>
       </c>
-      <c r="C344" s="2" t="s">
+      <c r="C344" s="1" t="s">
         <v>412</v>
       </c>
       <c r="D344" t="s">
@@ -9434,7 +9408,7 @@
       <c r="B345" t="s">
         <v>98</v>
       </c>
-      <c r="C345" s="2" t="s">
+      <c r="C345" s="1" t="s">
         <v>413</v>
       </c>
       <c r="D345" t="s">
@@ -9451,7 +9425,7 @@
       <c r="B346" t="s">
         <v>98</v>
       </c>
-      <c r="C346" s="2" t="s">
+      <c r="C346" s="1" t="s">
         <v>414</v>
       </c>
       <c r="D346" t="s">
@@ -9468,7 +9442,7 @@
       <c r="B347" t="s">
         <v>99</v>
       </c>
-      <c r="C347" s="2" t="s">
+      <c r="C347" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D347" t="s">
@@ -9485,7 +9459,7 @@
       <c r="B348" t="s">
         <v>99</v>
       </c>
-      <c r="C348" s="2" t="s">
+      <c r="C348" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D348" t="s">
@@ -9502,7 +9476,7 @@
       <c r="B349" t="s">
         <v>99</v>
       </c>
-      <c r="C349" s="2" t="s">
+      <c r="C349" s="1" t="s">
         <v>417</v>
       </c>
       <c r="D349" t="s">
@@ -9519,7 +9493,7 @@
       <c r="B350" t="s">
         <v>97</v>
       </c>
-      <c r="C350" s="2" t="s">
+      <c r="C350" s="1" t="s">
         <v>418</v>
       </c>
       <c r="D350" t="s">
@@ -9536,7 +9510,7 @@
       <c r="B351" t="s">
         <v>97</v>
       </c>
-      <c r="C351" s="2" t="s">
+      <c r="C351" s="1" t="s">
         <v>419</v>
       </c>
       <c r="D351" t="s">
@@ -9553,7 +9527,7 @@
       <c r="B352" t="s">
         <v>98</v>
       </c>
-      <c r="C352" s="2" t="s">
+      <c r="C352" s="1" t="s">
         <v>420</v>
       </c>
       <c r="D352" t="s">
@@ -9570,7 +9544,7 @@
       <c r="B353" t="s">
         <v>99</v>
       </c>
-      <c r="C353" s="2" t="s">
+      <c r="C353" s="1" t="s">
         <v>421</v>
       </c>
       <c r="D353" t="s">
@@ -9587,7 +9561,7 @@
       <c r="B354" t="s">
         <v>99</v>
       </c>
-      <c r="C354" s="2" t="s">
+      <c r="C354" s="1" t="s">
         <v>422</v>
       </c>
       <c r="D354" t="s">
@@ -9604,7 +9578,7 @@
       <c r="B355" t="s">
         <v>99</v>
       </c>
-      <c r="C355" s="2" t="s">
+      <c r="C355" s="1" t="s">
         <v>423</v>
       </c>
       <c r="D355" t="s">
@@ -9621,7 +9595,7 @@
       <c r="B356" t="s">
         <v>99</v>
       </c>
-      <c r="C356" s="2" t="s">
+      <c r="C356" s="1" t="s">
         <v>423</v>
       </c>
       <c r="D356" t="s">
@@ -9638,7 +9612,7 @@
       <c r="B357" t="s">
         <v>98</v>
       </c>
-      <c r="C357" s="2" t="s">
+      <c r="C357" s="1" t="s">
         <v>424</v>
       </c>
       <c r="D357" t="s">
@@ -9655,7 +9629,7 @@
       <c r="B358" t="s">
         <v>97</v>
       </c>
-      <c r="C358" s="2" t="s">
+      <c r="C358" s="1" t="s">
         <v>425</v>
       </c>
       <c r="D358" t="s">
@@ -9672,7 +9646,7 @@
       <c r="B359" t="s">
         <v>97</v>
       </c>
-      <c r="C359" s="2" t="s">
+      <c r="C359" s="1" t="s">
         <v>426</v>
       </c>
       <c r="D359" t="s">
@@ -9689,7 +9663,7 @@
       <c r="B360" t="s">
         <v>98</v>
       </c>
-      <c r="C360" s="2" t="s">
+      <c r="C360" s="1" t="s">
         <v>427</v>
       </c>
       <c r="D360" t="s">
@@ -9706,7 +9680,7 @@
       <c r="B361" t="s">
         <v>99</v>
       </c>
-      <c r="C361" s="2" t="s">
+      <c r="C361" s="1" t="s">
         <v>428</v>
       </c>
       <c r="D361" t="s">
@@ -9723,7 +9697,7 @@
       <c r="B362" t="s">
         <v>98</v>
       </c>
-      <c r="C362" s="2" t="s">
+      <c r="C362" s="1" t="s">
         <v>429</v>
       </c>
       <c r="D362" t="s">
@@ -9740,7 +9714,7 @@
       <c r="B363" t="s">
         <v>98</v>
       </c>
-      <c r="C363" s="2" t="s">
+      <c r="C363" s="1" t="s">
         <v>430</v>
       </c>
       <c r="D363" t="s">
@@ -9757,7 +9731,7 @@
       <c r="B364" t="s">
         <v>99</v>
       </c>
-      <c r="C364" s="2" t="s">
+      <c r="C364" s="1" t="s">
         <v>431</v>
       </c>
       <c r="D364" t="s">
@@ -9774,7 +9748,7 @@
       <c r="B365" t="s">
         <v>97</v>
       </c>
-      <c r="C365" s="2" t="s">
+      <c r="C365" s="1" t="s">
         <v>432</v>
       </c>
       <c r="D365" t="s">
@@ -9791,7 +9765,7 @@
       <c r="B366" t="s">
         <v>98</v>
       </c>
-      <c r="C366" s="2" t="s">
+      <c r="C366" s="1" t="s">
         <v>433</v>
       </c>
       <c r="D366" t="s">
@@ -9808,7 +9782,7 @@
       <c r="B367" t="s">
         <v>99</v>
       </c>
-      <c r="C367" s="2" t="s">
+      <c r="C367" s="1" t="s">
         <v>434</v>
       </c>
       <c r="D367" t="s">
@@ -9825,7 +9799,7 @@
       <c r="B368" t="s">
         <v>99</v>
       </c>
-      <c r="C368" s="2" t="s">
+      <c r="C368" s="1" t="s">
         <v>434</v>
       </c>
       <c r="D368" t="s">
@@ -9842,7 +9816,7 @@
       <c r="B369" t="s">
         <v>97</v>
       </c>
-      <c r="C369" s="2" t="s">
+      <c r="C369" s="1" t="s">
         <v>435</v>
       </c>
       <c r="D369" t="s">
@@ -9859,7 +9833,7 @@
       <c r="B370" t="s">
         <v>97</v>
       </c>
-      <c r="C370" s="2" t="s">
+      <c r="C370" s="1" t="s">
         <v>436</v>
       </c>
       <c r="D370" t="s">
@@ -9876,7 +9850,7 @@
       <c r="B371" t="s">
         <v>97</v>
       </c>
-      <c r="C371" s="2" t="s">
+      <c r="C371" s="1" t="s">
         <v>436</v>
       </c>
       <c r="D371" t="s">
